--- a/public/templates/TT-yeni.xlsx
+++ b/public/templates/TT-yeni.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$53</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t xml:space="preserve">Bakı şəhəri   </t>
   </si>
@@ -61,9 +61,6 @@
     <t>Ümumi dəyəri</t>
   </si>
   <si>
-    <t>kq</t>
-  </si>
-  <si>
     <t>Cəm</t>
   </si>
   <si>
@@ -91,29 +88,71 @@
     <t xml:space="preserve">Aşağıda qeyd olunan malların göndərilməsi haqqında çərçivə müqaviləsinin şərtlərinin əsasında sifariş olunmuşdur. </t>
   </si>
   <si>
-    <t>TƏHVİL TƏSLİM AKTI №366</t>
-  </si>
-  <si>
     <t xml:space="preserve">"AzRosPromİnvest” Məhdud Məsuliyyət  Cəmiyyəti                                                     </t>
   </si>
   <si>
-    <t>Şayba M24 (yaylı)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Şayba M24 </t>
-  </si>
-  <si>
-    <t>Bolt M24x100 (qara)</t>
-  </si>
-  <si>
-    <t>Qayka M24</t>
+    <t>Yeyə yastı</t>
+  </si>
+  <si>
+    <t>Ədəd </t>
+  </si>
+  <si>
+    <t>Daxili yiv M16</t>
+  </si>
+  <si>
+    <t>Ədəd</t>
+  </si>
+  <si>
+    <t>Daxili yiv M8</t>
+  </si>
+  <si>
+    <t>Daxili yiv M10</t>
+  </si>
+  <si>
+    <t>Sverlo 13.8 </t>
+  </si>
+  <si>
+    <t>Sverlo 6,8</t>
+  </si>
+  <si>
+    <t>Sverlo Konus 30</t>
+  </si>
+  <si>
+    <t>Sverlo  32</t>
+  </si>
+  <si>
+    <t>Sverlo 40   36</t>
+  </si>
+  <si>
+    <t>Sverlo 14</t>
+  </si>
+  <si>
+    <t> Xarici yiv  </t>
+  </si>
+  <si>
+    <t>Mərkəzi Burgu 3  3.15</t>
+  </si>
+  <si>
+    <t> Mərkəzi Burgu 4    </t>
+  </si>
+  <si>
+    <t>Mərkəzi Burgu 5   2.5</t>
+  </si>
+  <si>
+    <t>Frez slindr 14</t>
+  </si>
+  <si>
+    <t>Barmaq frez 16</t>
+  </si>
+  <si>
+    <t>TƏHVİL TƏSLİM AKTI №368</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,19 +194,21 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Droid Sans"/>
     </font>
   </fonts>
   <fills count="2">
@@ -178,7 +219,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -214,11 +255,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -229,18 +335,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -249,6 +348,9 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -261,17 +363,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -346,13 +482,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>43815</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -396,13 +532,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>98425</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>135255</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -708,127 +844,128 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="4" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="8.36328125" customWidth="1"/>
+    <col min="2" max="4" width="12.7265625" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="14"/>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="9" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="9" spans="1:7" ht="14.5" customHeight="1">
+      <c r="A9" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1"/>
-      <c r="G9" s="11">
+      <c r="G9" s="8">
         <v>46245</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-    </row>
-    <row r="13" spans="1:7" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="16" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="14.5" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="13" spans="1:7" ht="18.5" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="16" spans="1:7" ht="31.5" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="15"/>
+      <c r="C16" s="13"/>
       <c r="D16" s="2" t="s">
         <v>3</v>
       </c>
@@ -842,220 +979,491 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="17">
         <v>1</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="19">
+        <v>10</v>
+      </c>
+      <c r="F17" s="24">
+        <v>1.95</v>
+      </c>
+      <c r="G17" s="23">
+        <f>SUM(E17*F17)</f>
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1">
+      <c r="A18" s="20">
+        <v>2</v>
+      </c>
+      <c r="B18" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="8" t="s">
+      <c r="C18" s="29"/>
+      <c r="D18" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="22">
+        <v>2</v>
+      </c>
+      <c r="F18" s="24">
+        <v>11.7</v>
+      </c>
+      <c r="G18" s="23">
+        <f t="shared" ref="G18:G32" si="0">SUM(E18*F18)</f>
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1">
+      <c r="A19" s="20">
+        <v>3</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="26"/>
+      <c r="D19" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="22">
+        <v>3</v>
+      </c>
+      <c r="F19" s="24">
+        <v>13</v>
+      </c>
+      <c r="G19" s="23">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1">
+      <c r="A20" s="20">
+        <v>4</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="26"/>
+      <c r="D20" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="22">
+        <v>3</v>
+      </c>
+      <c r="F20" s="24">
+        <v>5.2</v>
+      </c>
+      <c r="G20" s="23">
+        <f t="shared" si="0"/>
+        <v>15.600000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1">
+      <c r="A21" s="20">
+        <v>5</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="26"/>
+      <c r="D21" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="22">
+        <v>3</v>
+      </c>
+      <c r="F21" s="24">
+        <v>11.7</v>
+      </c>
+      <c r="G21" s="23">
+        <f t="shared" si="0"/>
+        <v>35.099999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1">
+      <c r="A22" s="20">
+        <v>6</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="22">
+        <v>3</v>
+      </c>
+      <c r="F22" s="24">
+        <v>2.6</v>
+      </c>
+      <c r="G22" s="23">
+        <f t="shared" si="0"/>
+        <v>7.8000000000000007</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1">
+      <c r="A23" s="20">
         <v>7</v>
       </c>
-      <c r="E17" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="F17" s="10">
-        <v>5</v>
-      </c>
-      <c r="G17" s="10">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
+      <c r="B23" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="26"/>
+      <c r="D23" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="22">
+        <v>1</v>
+      </c>
+      <c r="F23" s="24">
+        <v>49.4</v>
+      </c>
+      <c r="G23" s="23">
+        <f t="shared" si="0"/>
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1">
+      <c r="A24" s="20">
+        <v>8</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="22">
+        <v>1</v>
+      </c>
+      <c r="F24" s="24">
+        <v>52</v>
+      </c>
+      <c r="G24" s="23">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1">
+      <c r="A25" s="20">
+        <v>9</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="22">
+        <v>1</v>
+      </c>
+      <c r="F25" s="24">
+        <v>58.5</v>
+      </c>
+      <c r="G25" s="23">
+        <f t="shared" si="0"/>
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1">
+      <c r="A26" s="20">
+        <v>10</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="22">
         <v>2</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="F26" s="24">
+        <v>13</v>
+      </c>
+      <c r="G26" s="23">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1">
+      <c r="A27" s="20">
+        <v>11</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="8" t="s">
+      <c r="E27" s="22">
+        <v>2</v>
+      </c>
+      <c r="F27" s="24">
+        <v>5.2</v>
+      </c>
+      <c r="G27" s="23">
+        <f t="shared" si="0"/>
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1">
+      <c r="A28" s="20">
+        <v>12</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="26"/>
+      <c r="D28" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="22">
+        <v>1</v>
+      </c>
+      <c r="F28" s="24">
+        <v>2.6</v>
+      </c>
+      <c r="G28" s="23">
+        <f t="shared" si="0"/>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1">
+      <c r="A29" s="20">
+        <v>13</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="26"/>
+      <c r="D29" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="22">
+        <v>1</v>
+      </c>
+      <c r="F29" s="24">
+        <v>2.6</v>
+      </c>
+      <c r="G29" s="23">
+        <f t="shared" si="0"/>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1">
+      <c r="A30" s="20">
+        <v>14</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="26"/>
+      <c r="D30" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="22">
+        <v>1</v>
+      </c>
+      <c r="F30" s="24">
+        <v>3.9</v>
+      </c>
+      <c r="G30" s="23">
+        <f t="shared" si="0"/>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1">
+      <c r="A31" s="20">
+        <v>15</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="26"/>
+      <c r="D31" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="22">
+        <v>2</v>
+      </c>
+      <c r="F31" s="24">
+        <v>10.4</v>
+      </c>
+      <c r="G31" s="23">
+        <f t="shared" si="0"/>
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1">
+      <c r="A32" s="20">
+        <v>16</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="22">
+        <v>1</v>
+      </c>
+      <c r="F32" s="24">
+        <v>13</v>
+      </c>
+      <c r="G32" s="23">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="F33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="F18" s="10">
-        <v>5</v>
-      </c>
-      <c r="G18" s="10">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>3</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="10">
-        <v>20</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="G33" s="7">
+        <f>SUM(G17:G32)</f>
+        <v>379.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="F34" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="10">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>4</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="10">
-        <v>5</v>
-      </c>
-      <c r="F20" s="10">
-        <v>8</v>
-      </c>
-      <c r="G20" s="10">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="10">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="4" t="s">
+      <c r="G34" s="25">
+        <f>SUM(G33*18%)</f>
+        <v>68.328000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="F35" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="10">
-        <v>38.700000000000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="4" t="s">
+      <c r="G35" s="25">
+        <f>SUM(G34,G33)</f>
+        <v>447.928</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.5">
+      <c r="A42" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="10">
-        <v>253.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="18" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="E42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="E27" s="18" t="s">
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+    </row>
+    <row r="43" spans="1:7" ht="14.5" customHeight="1">
+      <c r="A43" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="E43" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="E28" s="17" t="s">
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="19" t="s">
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="E48" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="E33" s="19" t="s">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="E51" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="E36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="E33:G34"/>
+  <mergeCells count="27">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A28:C29"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="A48:C49"/>
+    <mergeCell ref="E48:G49"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A13:G14"/>
     <mergeCell ref="A1:G7"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
